--- a/test/fixture/snapshot/cli/export-excel/by-kind.xlsx
+++ b/test/fixture/snapshot/cli/export-excel/by-kind.xlsx
@@ -563,6 +563,32 @@
     <comment ref="D5" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">Border: black
+Finish: normal
+Keywords:
+➤ Devoid</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Devoid (This card has no color.)
+Counter target spell unless its controller pays {1}. You create a 1/1 colorless Eldrazi Scion creature token. It has "Sacrifice this token: Add {C}." ({C} represents colorless mana.)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J5" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">➤ 2 generic
+➤ 1 blue</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0">
+      <text>
+        <r>
           <t xml:space="preserve">P/T: 5/4
 Border: borderless
 Finish: normal
@@ -571,7 +597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0">
+    <comment ref="E6" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Flying
@@ -580,7 +606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0">
+    <comment ref="J6" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 4 generic
@@ -588,7 +614,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0">
+    <comment ref="D7" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 7/7
@@ -599,7 +625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0">
+    <comment ref="E7" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Mutate {5}{U} (If you cast this spell for its mutate cost, put it over or under target non-Human creature you own. They mutate into the creature on top plus all abilities from under it.)
@@ -607,7 +633,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0">
+    <comment ref="J7" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 5 generic
@@ -615,7 +641,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0">
+    <comment ref="D8" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -623,7 +649,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0">
+    <comment ref="E8" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">(Gain the next level as a sorcery to add its ability.)
@@ -632,33 +658,6 @@
 When this Class becomes level 2, reveal cards from the top of your library until you reveal an artifact card. Put that card into your hand and the rest on the bottom of your library in a random order.
 {5}{U}: Level 3
 At the beginning of your end step, create a token that's a copy of target artifact you control.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J7" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">➤ 1 generic
-➤ 1 blue</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">Game Changer
-Border: black
-Finish: normal
-Keywords:
-➤ Overload</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">Return target nonland permanent you don't control to its owner's hand.
-Overload {6}{U} (You may cast this spell for its overload cost. If you do, change "target" in its text to "each.")</t>
         </r>
       </text>
     </comment>
@@ -673,20 +672,47 @@
     <comment ref="D9" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">Game Changer
+Border: black
+Finish: normal
+Keywords:
+➤ Overload</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Return target nonland permanent you don't control to its owner's hand.
+Overload {6}{U} (You may cast this spell for its overload cost. If you do, change "target" in its text to "each.")</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J9" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">➤ 1 generic
+➤ 1 blue</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0">
+      <text>
+        <r>
           <t xml:space="preserve">P/T: 3/3
 Border: black
 Finish: normal</t>
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <t>When this creature enters, double the number of each kind of counter on any number of target permanents.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="0">
+    <comment ref="J10" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 4 generic
@@ -694,7 +720,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0">
+    <comment ref="D11" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 2/2
@@ -705,14 +731,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0">
+    <comment ref="E11" authorId="0">
       <text>
         <r>
           <t>Avoidance — Whenever you cast a noncreature spell, exile up to one target nonland permanent you control, then return that card to the battlefield under its owner's control.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J10" authorId="0">
+    <comment ref="J11" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 3 generic
@@ -720,7 +746,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0">
+    <comment ref="D12" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -730,36 +756,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0">
+    <comment ref="E12" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">When this artifact enters, scry 2. (Look at the top two cards of your library, then put any number of them on the bottom and the rest on top in any order.)
 Whenever another artifact you control enters, this artifact becomes a 4/4 Phyrexian Eye artifact creature until end of turn.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J11" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">➤ 2 generic
-➤ 1 blue</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D12" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">Game Changer
-Border: black
-Finish: normal</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E12" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">If you control a commander, you may cast this spell without paying its mana cost.
-Counter target noncreature spell.</t>
         </r>
       </text>
     </comment>
@@ -774,18 +775,17 @@
     <comment ref="D13" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">P/T: 2/2
+          <t xml:space="preserve">Game Changer
 Border: black
-Finish: normal
-Keywords:
-➤ Proliferate</t>
+Finish: normal</t>
         </r>
       </text>
     </comment>
     <comment ref="E13" authorId="0">
       <text>
         <r>
-          <t>Whenever you cast a noncreature spell, proliferate. (Choose any number of permanents and/or players, then give each another counter of each kind already there.)</t>
+          <t xml:space="preserve">If you control a commander, you may cast this spell without paying its mana cost.
+Counter target noncreature spell.</t>
         </r>
       </text>
     </comment>
@@ -800,12 +800,38 @@
     <comment ref="D14" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">P/T: 2/2
+Border: black
+Finish: normal
+Keywords:
+➤ Proliferate</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0">
+      <text>
+        <r>
+          <t>Whenever you cast a noncreature spell, proliferate. (Choose any number of permanents and/or players, then give each another counter of each kind already there.)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J14" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">➤ 2 generic
+➤ 1 blue</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D15" authorId="0">
+      <text>
+        <r>
           <t xml:space="preserve">Border: black
 Finish: normal</t>
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0">
+    <comment ref="E15" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">If it's not your turn, you may exile a blue card from your hand rather than pay this spell's mana cost.
@@ -813,7 +839,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="0">
+    <comment ref="J15" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 generic
@@ -821,7 +847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="0">
+    <comment ref="D16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 1/1
@@ -833,7 +859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E15" authorId="0">
+    <comment ref="E16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Flying
@@ -841,7 +867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J15" authorId="0">
+    <comment ref="J16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 generic
@@ -849,7 +875,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D16" authorId="0">
+    <comment ref="D17" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Loyalty: 5
@@ -859,7 +885,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0">
+    <comment ref="E17" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Each opponent can't draw more than one card each turn.
@@ -867,7 +893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J16" authorId="0">
+    <comment ref="J17" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 generic
@@ -875,7 +901,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D17" authorId="0">
+    <comment ref="D18" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Loyalty: 4
@@ -884,7 +910,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0">
+    <comment ref="E18" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">+1: Tap target permanent. It doesn't untap during its controller's next untap step.
@@ -893,7 +919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J17" authorId="0">
+    <comment ref="J18" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 3 generic
@@ -901,7 +927,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D18" authorId="0">
+    <comment ref="D19" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 1/3
@@ -911,14 +937,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E18" authorId="0">
+    <comment ref="E19" authorId="0">
       <text>
         <r>
           <t>When this creature enters, look at the top X cards of your library, where X is your devotion to blue. Put up to one of them on top of your library and the rest on the bottom of your library in a random order. If X is greater than or equal to the number of cards in your library, you win the game. (Each {U} in the mana costs of permanents you control counts toward your devotion to blue.)</t>
         </r>
       </text>
     </comment>
-    <comment ref="J18" authorId="0">
+    <comment ref="J19" authorId="0">
       <text>
         <r>
           <t>➤ 2 blue</t>
@@ -1698,13 +1724,40 @@
     <comment ref="D3" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">Border: black
+Finish: normal
+Keywords:
+➤ Devoid</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Devoid (This card has no color.)
+Exile target nonland permanent. You may cast that card for as long as it remains exiled, and you may spend colorless mana as though it were mana of any color to cast that spell.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J3" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">➤ 2 generic
+➤ 1 white
+➤ 1 black</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0">
+      <text>
+        <r>
           <t xml:space="preserve">Loyalty: 5
 Border: black
 Finish: normal</t>
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0">
+    <comment ref="E4" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Creatures you control have vigilance.
@@ -1713,7 +1766,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="J4" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 generic
@@ -1722,7 +1775,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D4" authorId="0">
+    <comment ref="D5" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 2/4
@@ -1734,7 +1787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E4" authorId="0">
+    <comment ref="E5" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Flying
@@ -1743,7 +1796,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J4" authorId="0">
+    <comment ref="J5" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 generic
@@ -1752,7 +1805,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0">
+    <comment ref="D6" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1762,7 +1815,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0">
+    <comment ref="E6" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Create a 3/3 green Centaur creature token.
@@ -1773,7 +1826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0">
+    <comment ref="J6" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 3 generic
@@ -1783,7 +1836,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0">
+    <comment ref="D7" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Loyalty: 3
@@ -1792,7 +1845,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0">
+    <comment ref="E7" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">+1: Draw a card, then put a card from your hand on top of your library.
@@ -1802,7 +1855,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0">
+    <comment ref="J7" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 white
@@ -1811,7 +1864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0">
+    <comment ref="D8" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1819,14 +1872,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0">
+    <comment ref="E8" authorId="0">
       <text>
         <r>
           <t>Exile target nonland permanent. You lose 3 life.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="0">
+    <comment ref="J8" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 generic
@@ -1835,7 +1888,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0">
+    <comment ref="D9" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Loyalty: 5
@@ -1846,7 +1899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0">
+    <comment ref="E9" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Spells and abilities your opponents control can't cause their controller to search their library.
@@ -1854,7 +1907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J8" authorId="0">
+    <comment ref="J9" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 generic
@@ -1862,7 +1915,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="0">
+    <comment ref="D10" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1870,14 +1923,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <t>Destroy target permanent an opponent controls. Its controller may search their library for a basic land card, put it onto the battlefield, then shuffle.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="0">
+    <comment ref="J10" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 black
@@ -1885,7 +1938,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0">
+    <comment ref="D11" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1895,14 +1948,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0">
+    <comment ref="E11" authorId="0">
       <text>
         <r>
           <t>Destroy target nonland permanent. Proliferate. (Choose any number of permanents and/or players, then give each another counter of each kind already there.)</t>
         </r>
       </text>
     </comment>
-    <comment ref="J10" authorId="0">
+    <comment ref="J11" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 generic
@@ -1911,7 +1964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0">
+    <comment ref="D12" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 7/7
@@ -1925,7 +1978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0">
+    <comment ref="E12" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Flying, vigilance, deathtouch, lifelink
@@ -1933,7 +1986,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J11" authorId="0">
+    <comment ref="J12" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 3 generic
@@ -1944,7 +1997,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0">
+    <comment ref="D13" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 4/4
@@ -1959,7 +2012,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0">
+    <comment ref="E13" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Flying, vigilance, deathtouch, lifelink
@@ -1967,7 +2020,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="0">
+    <comment ref="J13" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 green
@@ -1977,7 +2030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0">
+    <comment ref="D14" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 3/2
@@ -1988,7 +2041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0">
+    <comment ref="E14" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Menace
@@ -1996,7 +2049,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="0">
+    <comment ref="J14" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 generic
@@ -2005,7 +2058,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0">
+    <comment ref="D15" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -2013,14 +2066,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0">
+    <comment ref="E15" authorId="0">
       <text>
         <r>
           <t>Whenever a creature you control with a +1/+1 counter on it deals combat damage to a player, you may draw a card.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="0">
+    <comment ref="J15" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 generic
@@ -2029,7 +2082,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="0">
+    <comment ref="D16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 3/4
@@ -2042,7 +2095,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E15" authorId="0">
+    <comment ref="E16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Whenever you cast a Phyrexian creature or artifact creature spell, incubate X, where X is that spell's mana value. (Create an Incubator token with X +1/+1 counters on it and "{2}: Transform this token." It transforms into a 0/0 Phyrexian artifact creature.)
@@ -2050,7 +2103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J15" authorId="0">
+    <comment ref="J16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 generic
@@ -2059,7 +2112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D16" authorId="0">
+    <comment ref="D17" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 3/5
@@ -2068,7 +2121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0">
+    <comment ref="E17" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Whenever Carth enters or a planeswalker you control dies, look at the top seven cards of your library. You may reveal a planeswalker card from among them and put it into your hand. Put the rest on the bottom of your library in a random order.
@@ -2076,7 +2129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J16" authorId="0">
+    <comment ref="J17" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 generic
@@ -2085,7 +2138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D17" authorId="0">
+    <comment ref="D18" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 1/2
@@ -2094,7 +2147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0">
+    <comment ref="E18" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">{T}: Exile target land card from a graveyard. Add one mana of any color.
@@ -2103,35 +2156,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="J17" authorId="0">
+    <comment ref="J18" authorId="0">
       <text>
         <r>
           <t>➤ 1× black or green</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D18" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">Border: black
-Finish: normal</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E18" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">When this enchantment enters, you may exile target nonland permanent not named Detention Sphere and all other permanents with the same name as that permanent.
-When this enchantment leaves the battlefield, return the exiled cards to the battlefield under their owner's control.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J18" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">➤ 1 generic
-➤ 1 white
-➤ 1 blue</t>
         </r>
       </text>
     </comment>
@@ -2146,17 +2174,17 @@
     <comment ref="E19" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">Choose one —
-• Counter target spell with mana value less than or equal to the number of cards in its controller's graveyard.
-• Destroy target creature with mana value less than or equal to the number of cards in its controller's graveyard.</t>
+          <t xml:space="preserve">When this enchantment enters, you may exile target nonland permanent not named Detention Sphere and all other permanents with the same name as that permanent.
+When this enchantment leaves the battlefield, return the exiled cards to the battlefield under their owner's control.</t>
         </r>
       </text>
     </comment>
     <comment ref="J19" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">➤ 1 blue
-➤ 1 black</t>
+          <t xml:space="preserve">➤ 1 generic
+➤ 1 white
+➤ 1 blue</t>
         </r>
       </text>
     </comment>
@@ -2171,11 +2199,36 @@
     <comment ref="E20" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">Choose one —
+• Counter target spell with mana value less than or equal to the number of cards in its controller's graveyard.
+• Destroy target creature with mana value less than or equal to the number of cards in its controller's graveyard.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J20" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">➤ 1 blue
+➤ 1 black</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D21" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Border: black
+Finish: normal</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0">
+      <text>
+        <r>
           <t>Return any number of permanent cards with different names from your graveyard to the battlefield.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J20" authorId="0">
+    <comment ref="J21" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 white
@@ -2184,7 +2237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D21" authorId="0">
+    <comment ref="D22" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 3/3
@@ -2195,7 +2248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0">
+    <comment ref="E22" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">When Ezuri enters, you may pay {3}. If you do, proliferate twice.
@@ -2203,7 +2256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J21" authorId="0">
+    <comment ref="J22" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 generic
@@ -2212,7 +2265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D22" authorId="0">
+    <comment ref="D23" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 3/5
@@ -2224,37 +2277,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="E22" authorId="0">
+    <comment ref="E23" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">At the beginning of combat on your turn, choose one —
 • Incubate 2 twice. (To incubate 2, create an Incubator token with two +1/+1 counters on it and "{2}: Transform this token." It transforms into a 0/0 Phyrexian artifact creature.)
 • Transform all Incubator tokens you control.
 • Phyrexians you control gain first strike and deathtouch until end of turn.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J22" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">➤ 3 generic
-➤ 1 black
-➤ 1 green</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D23" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">Border: black
-Finish: normal</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E23" authorId="0">
-      <text>
-        <r>
-          <t>Whenever a creature you control dies, you gain 1 life and draw a card.</t>
         </r>
       </text>
     </comment>
@@ -2270,8 +2299,7 @@
     <comment ref="D24" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">P/T: 6/6
-Border: black
+          <t xml:space="preserve">Border: black
 Finish: normal</t>
         </r>
       </text>
@@ -2279,11 +2307,36 @@
     <comment ref="E24" authorId="0">
       <text>
         <r>
+          <t>Whenever a creature you control dies, you gain 1 life and draw a card.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J24" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">➤ 3 generic
+➤ 1 black
+➤ 1 green</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D25" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">P/T: 6/6
+Border: black
+Finish: normal</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E25" authorId="0">
+      <text>
+        <r>
           <t>During each of your turns, you may play a land and cast a permanent spell of each permanent type from your graveyard. (If a card has multiple permanent types, choose one as you play it.)</t>
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="0">
+    <comment ref="J25" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 3 generic
@@ -2293,7 +2346,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D25" authorId="0">
+    <comment ref="D26" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -2301,7 +2354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E25" authorId="0">
+    <comment ref="E26" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">{1}{G}{U}: Put a +1/+1 counter on target creature you control.
@@ -2310,7 +2363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0">
+    <comment ref="J26" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 green
@@ -2318,7 +2371,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0">
+    <comment ref="D27" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 1/3
@@ -2329,7 +2382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E26" authorId="0">
+    <comment ref="E27" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Commander ninjutsu {U}{B} ({U}{B}, Return an unblocked attacker you control to hand: Put this card onto the battlefield from your hand or the command zone tapped and attacking.)
@@ -2337,7 +2390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0">
+    <comment ref="J27" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 generic
@@ -2346,7 +2399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D27" authorId="0">
+    <comment ref="D28" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">P/T: 2/2
@@ -2355,7 +2408,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0">
+    <comment ref="E28" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">{G}{U}: This turn, each creature you control enters with an additional +1/+1 counter on it.
@@ -2363,7 +2416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0">
+    <comment ref="J28" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 green
@@ -2823,12 +2876,28 @@
     <comment ref="E11" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">{T}: Add {C}. ({C} represents colorless mana.)
+{T}, Pay 1 life: Add one mana of any color. Spend this mana only to cast a spell with devoid.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Border: black
+Finish: normal</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0">
+      <text>
+        <r>
           <t xml:space="preserve">This land enters tapped.
 {T}: Add {U} or {B}.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0">
+    <comment ref="D13" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -2838,28 +2907,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0">
+    <comment ref="E13" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">{T}: Add {W}.
 Channel — {2}{W}, Discard this card: It deals 4 damage to target attacking or blocking creature. This ability costs {1} less to activate for each legendary creature you control.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D13" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">Border: black
-Finish: normal</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E13" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">As this land enters, you may reveal a Soldier card from your hand. This land enters tapped unless you revealed a Soldier card this way or you control a Soldier.
-{T}: Add {W} or {U}.
-{5}, {T}: Soldiers you control get +1/+1 until end of turn.</t>
         </r>
       </text>
     </comment>
@@ -2874,12 +2926,29 @@
     <comment ref="E14" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">As this land enters, you may reveal a Soldier card from your hand. This land enters tapped unless you revealed a Soldier card this way or you control a Soldier.
+{T}: Add {W} or {U}.
+{5}, {T}: Soldiers you control get +1/+1 until end of turn.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D15" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Border: black
+Finish: normal</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E15" authorId="0">
+      <text>
+        <r>
           <t xml:space="preserve">{T}: Add {C}.
 {1}, {T}: Add one mana of any color. If that mana is spent on a multicolored creature spell, that creature enters with an additional +1/+1 counter on it.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="0">
+    <comment ref="D16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -2889,7 +2958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E15" authorId="0">
+    <comment ref="E16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">({T}: Add {W}, {B}, or {G}.)
@@ -2898,7 +2967,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D16" authorId="0">
+    <comment ref="D17" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -2906,14 +2975,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0">
+    <comment ref="E17" authorId="0">
       <text>
         <r>
           <t>{T}, Pay 1 life: Add one mana of any color.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D17" authorId="0">
+    <comment ref="D18" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -2923,7 +2992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0">
+    <comment ref="E18" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">This land enters tapped.
@@ -2931,7 +3000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D18" authorId="0">
+    <comment ref="D19" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -2939,14 +3008,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E18" authorId="0">
+    <comment ref="E19" authorId="0">
       <text>
         <r>
           <t>{T}, Pay 1 life, Sacrifice this land: Search your library for a basic land card, put it onto the battlefield, then shuffle.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D19" authorId="0">
+    <comment ref="D20" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: borderless
@@ -2956,7 +3025,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0">
+    <comment ref="E20" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">({T}: Add {W}, {U}, or {B}.)
@@ -2965,7 +3034,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D20" authorId="0">
+    <comment ref="D21" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -2973,7 +3042,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0">
+    <comment ref="E21" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">This land enters tapped unless you have two or more opponents.
@@ -2981,7 +3050,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D21" authorId="0">
+    <comment ref="D22" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -2991,7 +3060,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0">
+    <comment ref="E22" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">({T}: Add {G}, {W}, or {U}.)
@@ -3000,7 +3069,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D22" authorId="0">
+    <comment ref="D23" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -3010,7 +3079,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E22" authorId="0">
+    <comment ref="E23" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">This land enters tapped.
@@ -3019,7 +3088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D23" authorId="0">
+    <comment ref="D24" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -3029,30 +3098,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="E23" authorId="0">
+    <comment ref="E24" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">({T}: Add {U} or {B}.)
 This land enters tapped.
 When this land enters, surveil 1. (Look at the top card of your library. You may put it into your graveyard.)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D24" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">Border: black
-Finish: normal</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E24" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">(As this Saga enters and after your draw step, add a lore counter. Sacrifice after III.)
-I — This Saga gains "{T}: Add {C}."
-II — This Saga gains "{2}, {T}: Create a 0/0 colorless Construct artifact creature token with 'This token gets +1/+1 for each artifact you control.'"
-III — Search your library for an artifact card with mana cost {0} or {1}, put it onto the battlefield, then shuffle.</t>
         </r>
       </text>
     </comment>
@@ -3067,8 +3118,10 @@
     <comment ref="E25" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">This land enters tapped unless you have two or more opponents.
-{T}: Add {W} or {B}.</t>
+          <t xml:space="preserve">(As this Saga enters and after your draw step, add a lore counter. Sacrifice after III.)
+I — This Saga gains "{T}: Add {C}."
+II — This Saga gains "{2}, {T}: Create a 0/0 colorless Construct artifact creature token with 'This token gets +1/+1 for each artifact you control.'"
+III — Search your library for an artifact card with mana cost {0} or {1}, put it onto the battlefield, then shuffle.</t>
         </r>
       </text>
     </comment>
@@ -3083,11 +3136,27 @@
     <comment ref="E26" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">This land enters tapped unless you have two or more opponents.
+{T}: Add {W} or {B}.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D27" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Border: black
+Finish: normal</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E27" authorId="0">
+      <text>
+        <r>
           <t>Each land is a Forest in addition to its other land types.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D27" authorId="0">
+    <comment ref="D28" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -3097,7 +3166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0">
+    <comment ref="E28" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">({T}: Add {B}, {G}, or {U}.)
@@ -3111,7 +3180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="755">
   <si>
     <t>Commander (All) - White</t>
   </si>
@@ -3548,6 +3617,30 @@
     <t>Open Aberrant Researcher // Perfected Form</t>
   </si>
   <si>
+    <t>Abstruse Interference</t>
+  </si>
+  <si>
+    <t>ogw</t>
+  </si>
+  <si>
+    <t>Oath of the Gatewatch</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>{2}{U}</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>Open Abstruse Interference</t>
+  </si>
+  <si>
     <t>All-Seeing Arbiter</t>
   </si>
   <si>
@@ -3584,9 +3677,6 @@
     <t>{5}{U}{U}</t>
   </si>
   <si>
-    <t>0.09</t>
-  </si>
-  <si>
     <t>Open Archipelagore</t>
   </si>
   <si>
@@ -3623,9 +3713,6 @@
     <t>Ravnica Remastered</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>42.01</t>
   </si>
   <si>
@@ -3683,9 +3770,6 @@
     <t>50</t>
   </si>
   <si>
-    <t>{2}{U}</t>
-  </si>
-  <si>
     <t>0.03</t>
   </si>
   <si>
@@ -4058,9 +4142,6 @@
     <t>{2}{B}</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Open Painful Truths</t>
   </si>
   <si>
@@ -4364,6 +4445,24 @@
     <t>Commander (All) - Multicolor</t>
   </si>
   <si>
+    <t>Abstruse Appropriation</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>{2}{W}{B}</t>
+  </si>
+  <si>
+    <t>B, W</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Open Abstruse Appropriation</t>
+  </si>
+  <si>
     <t>Ajani, the Greathearted</t>
   </si>
   <si>
@@ -4466,9 +4565,6 @@
     <t>{1}{W}{B}</t>
   </si>
   <si>
-    <t>B, W</t>
-  </si>
-  <si>
     <t>2.07</t>
   </si>
   <si>
@@ -4607,9 +4703,6 @@
     <t>2</t>
   </si>
   <si>
-    <t>{2}{W}{B}</t>
-  </si>
-  <si>
     <t>Open Brimaz, Blight of Oreskos</t>
   </si>
   <si>
@@ -5106,6 +5199,18 @@
   </si>
   <si>
     <t>Open Command Tower</t>
+  </si>
+  <si>
+    <t>Corrupted Crossroads</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Open Corrupted Crossroads</t>
   </si>
   <si>
     <t>Dimir Guildgate</t>
@@ -10144,7 +10249,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O218"/>
+  <dimension ref="A1:O219"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -10334,31 +10439,31 @@
         <v>17</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7">
+        <v>3</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="K5" s="7">
-        <v>6</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>142</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>142</v>
@@ -10387,22 +10492,22 @@
         <v>154</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K6" s="11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>142</v>
@@ -10411,15 +10516,15 @@
         <v>142</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B7" s="7">
         <v>1</v>
@@ -10428,19 +10533,19 @@
         <v>17</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>163</v>
@@ -10449,7 +10554,7 @@
         <v>164</v>
       </c>
       <c r="K7" s="7">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>142</v>
@@ -10458,15 +10563,15 @@
         <v>142</v>
       </c>
       <c r="N7" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="O7" s="7" t="s">
         <v>165</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" s="11">
         <v>1</v>
@@ -10475,13 +10580,13 @@
         <v>17</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>168</v>
@@ -10493,7 +10598,7 @@
         <v>170</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="K8" s="11">
         <v>2</v>
@@ -10505,15 +10610,15 @@
         <v>142</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B9" s="7">
         <v>1</v>
@@ -10522,28 +10627,28 @@
         <v>17</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>174</v>
+        <v>40</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>51</v>
+        <v>175</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>52</v>
+        <v>176</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K9" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>142</v>
@@ -10578,10 +10683,10 @@
         <v>20</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>161</v>
+        <v>51</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>162</v>
+        <v>52</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>181</v>
@@ -10590,7 +10695,7 @@
         <v>182</v>
       </c>
       <c r="K10" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10" s="11" t="s">
         <v>142</v>
@@ -10616,28 +10721,28 @@
         <v>17</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>186</v>
+        <v>65</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>186</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="G11" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>190</v>
-      </c>
       <c r="K11" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>142</v>
@@ -10646,15 +10751,15 @@
         <v>142</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B12" s="11">
         <v>1</v>
@@ -10663,25 +10768,25 @@
         <v>17</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>51</v>
+        <v>193</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>52</v>
+        <v>194</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="K12" s="11">
         <v>3</v>
@@ -10693,15 +10798,15 @@
         <v>142</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B13" s="7">
         <v>1</v>
@@ -10710,25 +10815,25 @@
         <v>17</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>198</v>
+        <v>51</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="J13" s="7" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="K13" s="7">
         <v>3</v>
@@ -10757,13 +10862,13 @@
         <v>17</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>203</v>
@@ -10772,10 +10877,10 @@
         <v>204</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>205</v>
+        <v>149</v>
       </c>
       <c r="K14" s="11">
         <v>3</v>
@@ -10787,15 +10892,15 @@
         <v>142</v>
       </c>
       <c r="N14" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="O14" s="11" t="s">
         <v>206</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B15" s="7">
         <v>1</v>
@@ -10804,25 +10909,25 @@
         <v>17</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>114</v>
-      </c>
       <c r="I15" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>210</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>190</v>
       </c>
       <c r="K15" s="7">
         <v>3</v>
@@ -10851,25 +10956,25 @@
         <v>17</v>
       </c>
       <c r="D16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="F16" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="I16" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>218</v>
-      </c>
       <c r="J16" s="11" t="s">
-        <v>205</v>
+        <v>149</v>
       </c>
       <c r="K16" s="11">
         <v>3</v>
@@ -10881,15 +10986,15 @@
         <v>142</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B17" s="7">
         <v>1</v>
@@ -10898,28 +11003,28 @@
         <v>17</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E17" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" s="7" t="s">
+      <c r="I17" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>225</v>
-      </c>
       <c r="J17" s="7" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="K17" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>142</v>
@@ -10928,75 +11033,105 @@
         <v>142</v>
       </c>
       <c r="N17" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B18" s="11">
+        <v>1</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="O17" s="7" t="s">
+      <c r="F18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="11" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="H18" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="B18" s="15">
+      <c r="I18" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="K18" s="11">
+        <v>5</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="N18" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="B19" s="13">
         <v>1</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C19" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D19" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="F18" s="15" t="s">
+      <c r="E19" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="K18" s="15">
+      <c r="G19" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="K19" s="13">
         <v>2</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="L19" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="M18" s="15" t="s">
+      <c r="M19" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="N18" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="O18" s="15" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+      <c r="N19" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -14380,6 +14515,23 @@
       <c r="M218" s="1"/>
       <c r="N218" s="1"/>
       <c r="O218" s="1"/>
+    </row>
+    <row r="219" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
+      <c r="E219" s="1"/>
+      <c r="F219" s="1"/>
+      <c r="G219" s="1"/>
+      <c r="H219" s="1"/>
+      <c r="I219" s="1"/>
+      <c r="J219" s="1"/>
+      <c r="K219" s="1"/>
+      <c r="L219" s="1"/>
+      <c r="M219" s="1"/>
+      <c r="N219" s="1"/>
+      <c r="O219" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -14402,10 +14554,11 @@
     <hyperlink ref="O16" r:id="rId14"/>
     <hyperlink ref="O17" r:id="rId15"/>
     <hyperlink ref="O18" r:id="rId16"/>
+    <hyperlink ref="O19" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId18"/>
+  <legacyDrawing r:id="rId19"/>
 </worksheet>
 </file>
 
@@ -14432,7 +14585,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14498,7 +14651,7 @@
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B3" s="7">
         <v>1</v>
@@ -14510,42 +14663,42 @@
         <v>58</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K3" s="7">
         <v>3</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B4" s="9">
         <v>1</v>
@@ -14557,42 +14710,42 @@
         <v>58</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>50</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K4" s="9">
         <v>3</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B5" s="7">
         <v>1</v>
@@ -14601,45 +14754,45 @@
         <v>17</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K5" s="7">
         <v>2</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B6" s="11">
         <v>1</v>
@@ -14657,36 +14810,36 @@
         <v>20</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K6" s="11">
         <v>1</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B7" s="7">
         <v>1</v>
@@ -14695,45 +14848,45 @@
         <v>17</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K7" s="7">
         <v>6</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B8" s="11">
         <v>1</v>
@@ -14745,42 +14898,42 @@
         <v>48</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K8" s="11">
         <v>3</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B9" s="7">
         <v>1</v>
@@ -14792,42 +14945,42 @@
         <v>65</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>32</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K9" s="7">
         <v>4</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N9" s="7" t="s">
         <v>37</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B10" s="11">
         <v>1</v>
@@ -14839,42 +14992,42 @@
         <v>65</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K10" s="11">
         <v>4</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B11" s="7">
         <v>1</v>
@@ -14898,30 +15051,30 @@
         <v>52</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K11" s="7">
         <v>4</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B12" s="11">
         <v>1</v>
@@ -14939,36 +15092,36 @@
         <v>32</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K12" s="11">
         <v>2</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B13" s="7">
         <v>1</v>
@@ -14986,36 +15139,36 @@
         <v>32</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>295</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="K13" s="7">
         <v>2</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B14" s="11">
         <v>1</v>
@@ -15033,36 +15186,36 @@
         <v>20</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K14" s="11">
         <v>5</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B15" s="7">
         <v>1</v>
@@ -15074,42 +15227,42 @@
         <v>65</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I15" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>308</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>303</v>
       </c>
       <c r="K15" s="7">
         <v>5</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N15" s="7" t="s">
         <v>37</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B16" s="11">
         <v>1</v>
@@ -15127,36 +15280,36 @@
         <v>20</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K16" s="11">
         <v>3</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B17" s="7">
         <v>1</v>
@@ -15165,45 +15318,45 @@
         <v>17</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K17" s="7">
         <v>2</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B18" s="11">
         <v>1</v>
@@ -15215,42 +15368,42 @@
         <v>48</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K18" s="11">
         <v>8</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B19" s="7">
         <v>1</v>
@@ -15262,42 +15415,42 @@
         <v>48</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K19" s="7">
         <v>4</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B20" s="15">
         <v>1</v>
@@ -15315,31 +15468,31 @@
         <v>87</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="K20" s="15">
         <v>1</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N20" s="15" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="O20" s="15" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -18794,7 +18947,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18860,7 +19013,7 @@
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B3" s="13">
         <v>1</v>
@@ -18872,37 +19025,37 @@
         <v>30</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="K3" s="13">
         <v>3</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -22340,7 +22493,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22406,7 +22559,7 @@
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B3" s="7">
         <v>1</v>
@@ -22418,42 +22571,42 @@
         <v>65</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="K3" s="7">
         <v>3</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
@@ -22465,7 +22618,7 @@
         <v>48</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>50</v>
@@ -22477,30 +22630,30 @@
         <v>98</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="K4" s="11">
         <v>3</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B5" s="7">
         <v>1</v>
@@ -22512,42 +22665,42 @@
         <v>65</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K5" s="7">
         <v>5</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B6" s="11">
         <v>1</v>
@@ -22565,36 +22718,36 @@
         <v>20</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="K6" s="11">
         <v>3</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B7" s="7">
         <v>1</v>
@@ -22606,42 +22759,42 @@
         <v>30</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K7" s="7">
         <v>2</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N7" s="7" t="s">
         <v>62</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B8" s="11">
         <v>1</v>
@@ -22650,45 +22803,45 @@
         <v>17</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="K8" s="11">
         <v>4</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B9" s="7">
         <v>1</v>
@@ -22697,10 +22850,10 @@
         <v>17</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>50</v>
@@ -22712,30 +22865,30 @@
         <v>52</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="K9" s="7">
         <v>9</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B10" s="15">
         <v>1</v>
@@ -22747,37 +22900,37 @@
         <v>48</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>50</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="K10" s="15">
         <v>6</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -26202,7 +26355,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O227"/>
+  <dimension ref="A1:O228"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -26223,7 +26376,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -26289,7 +26442,7 @@
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B3" s="7">
         <v>1</v>
@@ -26298,45 +26451,45 @@
         <v>17</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>214</v>
+        <v>40</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>418</v>
+        <v>40</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K3" s="7">
         <v>4</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>421</v>
+        <v>150</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
@@ -26345,45 +26498,45 @@
         <v>17</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>381</v>
+        <v>203</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>382</v>
+        <v>204</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K4" s="11">
         <v>4</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B5" s="7">
         <v>1</v>
@@ -26392,45 +26545,45 @@
         <v>17</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>433</v>
+        <v>385</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>434</v>
+        <v>386</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K5" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B6" s="11">
         <v>1</v>
@@ -26439,45 +26592,45 @@
         <v>17</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>203</v>
+        <v>443</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>204</v>
+        <v>444</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="K6" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B7" s="7">
         <v>1</v>
@@ -26486,45 +26639,45 @@
         <v>17</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>40</v>
+        <v>219</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>40</v>
+        <v>450</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>447</v>
+        <v>208</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>448</v>
+        <v>209</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K7" s="7">
         <v>3</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B8" s="11">
         <v>1</v>
@@ -26533,45 +26686,45 @@
         <v>17</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>214</v>
+        <v>40</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>455</v>
+        <v>40</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>198</v>
+        <v>457</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>199</v>
+        <v>458</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="K8" s="11">
         <v>3</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B9" s="7">
         <v>1</v>
@@ -26580,45 +26733,45 @@
         <v>17</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>40</v>
+        <v>219</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>40</v>
+        <v>464</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>349</v>
+        <v>203</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>350</v>
+        <v>204</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K9" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B10" s="11">
         <v>1</v>
@@ -26636,36 +26789,36 @@
         <v>20</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>466</v>
+        <v>353</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>467</v>
+        <v>354</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>194</v>
+        <v>470</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K10" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B11" s="7">
         <v>1</v>
@@ -26674,45 +26827,45 @@
         <v>17</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>472</v>
+        <v>40</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>187</v>
+        <v>475</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>188</v>
+        <v>476</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>473</v>
+        <v>199</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K11" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>475</v>
+        <v>373</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>475</v>
+        <v>373</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>62</v>
+        <v>478</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B12" s="11">
         <v>1</v>
@@ -26724,42 +26877,42 @@
         <v>48</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K12" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>481</v>
+        <v>62</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B13" s="7">
         <v>1</v>
@@ -26771,42 +26924,42 @@
         <v>48</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>427</v>
+        <v>489</v>
       </c>
       <c r="K13" s="7">
         <v>4</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>428</v>
+        <v>484</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>428</v>
+        <v>484</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B14" s="11">
         <v>1</v>
@@ -26815,45 +26968,45 @@
         <v>17</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>30</v>
+        <v>493</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>489</v>
+        <v>236</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>490</v>
+        <v>237</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>368</v>
+        <v>494</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>491</v>
+        <v>437</v>
       </c>
       <c r="K14" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>492</v>
+        <v>438</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>492</v>
+        <v>438</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B15" s="7">
         <v>1</v>
@@ -26862,45 +27015,45 @@
         <v>17</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>496</v>
+        <v>30</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>67</v>
+        <v>498</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>68</v>
+        <v>499</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>497</v>
+        <v>372</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K15" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>451</v>
+        <v>501</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>451</v>
+        <v>501</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>401</v>
+        <v>502</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B16" s="11">
         <v>1</v>
@@ -26912,42 +27065,42 @@
         <v>48</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>468</v>
+        <v>423</v>
       </c>
       <c r="K16" s="11">
         <v>4</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>369</v>
+        <v>424</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>369</v>
+        <v>424</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B17" s="7">
         <v>1</v>
@@ -26956,37 +27109,37 @@
         <v>17</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>506</v>
+        <v>97</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>507</v>
+        <v>98</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>509</v>
+        <v>477</v>
       </c>
       <c r="K17" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>510</v>
+        <v>358</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>511</v>
@@ -27003,34 +27156,34 @@
         <v>17</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>30</v>
+        <v>513</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K18" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>517</v>
+        <v>373</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>517</v>
+        <v>373</v>
       </c>
       <c r="N18" s="11" t="s">
         <v>518</v>
@@ -27050,45 +27203,45 @@
         <v>17</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>161</v>
+        <v>521</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>162</v>
+        <v>522</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K19" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>428</v>
+        <v>525</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>428</v>
+        <v>525</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B20" s="11">
         <v>1</v>
@@ -27097,45 +27250,45 @@
         <v>17</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>419</v>
+        <v>529</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="K20" s="11">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>527</v>
+        <v>438</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>527</v>
+        <v>438</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="21" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B21" s="7">
         <v>1</v>
@@ -27144,45 +27297,45 @@
         <v>17</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>531</v>
+        <v>58</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>187</v>
+        <v>75</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>188</v>
+        <v>76</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>532</v>
+        <v>429</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K21" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>492</v>
+        <v>535</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>492</v>
+        <v>535</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B22" s="11">
         <v>1</v>
@@ -27194,42 +27347,42 @@
         <v>48</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>396</v>
+        <v>193</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>397</v>
+        <v>194</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K22" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>369</v>
+        <v>501</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>369</v>
+        <v>501</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B23" s="7">
         <v>1</v>
@@ -27238,45 +27391,45 @@
         <v>17</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>30</v>
+        <v>545</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>543</v>
+        <v>400</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>544</v>
+        <v>401</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="K23" s="7">
         <v>5</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="24" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B24" s="11">
         <v>1</v>
@@ -27285,45 +27438,45 @@
         <v>17</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>549</v>
+        <v>30</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>113</v>
+        <v>551</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>114</v>
+        <v>552</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="K24" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>552</v>
+        <v>373</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>552</v>
+        <v>373</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B25" s="7">
         <v>1</v>
@@ -27332,45 +27485,45 @@
         <v>17</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>30</v>
+        <v>557</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>300</v>
+        <v>113</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>301</v>
+        <v>114</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="K25" s="7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>492</v>
+        <v>560</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>492</v>
+        <v>560</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="26" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B26" s="11">
         <v>1</v>
@@ -27379,105 +27532,135 @@
         <v>17</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>561</v>
+        <v>30</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>562</v>
+        <v>305</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>563</v>
+        <v>306</v>
       </c>
       <c r="I26" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="K26" s="11">
+        <v>2</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="N26" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="B27" s="7">
+        <v>1</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="J26" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="K26" s="11">
+      <c r="J27" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="K27" s="7">
         <v>3</v>
       </c>
-      <c r="L26" s="11" t="s">
-        <v>428</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>428</v>
-      </c>
-      <c r="N26" s="11" t="s">
+      <c r="L27" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>575</v>
+      </c>
+      <c r="B28" s="15">
+        <v>1</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>579</v>
+      </c>
+      <c r="J28" s="15" t="s">
         <v>565</v>
       </c>
-      <c r="O26" s="11" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="B27" s="13">
-        <v>1</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>569</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>571</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>557</v>
-      </c>
-      <c r="K27" s="13">
+      <c r="K28" s="15">
         <v>2</v>
       </c>
-      <c r="L27" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="M27" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="N27" s="13" t="s">
-        <v>572</v>
-      </c>
-      <c r="O27" s="13" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
+      <c r="L28" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="N28" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="O28" s="15" t="s">
+        <v>581</v>
+      </c>
     </row>
     <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
@@ -30861,6 +31044,23 @@
       <c r="M227" s="1"/>
       <c r="N227" s="1"/>
       <c r="O227" s="1"/>
+    </row>
+    <row r="228" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="1"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
+      <c r="E228" s="1"/>
+      <c r="F228" s="1"/>
+      <c r="G228" s="1"/>
+      <c r="H228" s="1"/>
+      <c r="I228" s="1"/>
+      <c r="J228" s="1"/>
+      <c r="K228" s="1"/>
+      <c r="L228" s="1"/>
+      <c r="M228" s="1"/>
+      <c r="N228" s="1"/>
+      <c r="O228" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -30892,10 +31092,11 @@
     <hyperlink ref="O25" r:id="rId23"/>
     <hyperlink ref="O26" r:id="rId24"/>
     <hyperlink ref="O27" r:id="rId25"/>
+    <hyperlink ref="O28" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId27"/>
+  <legacyDrawing r:id="rId28"/>
 </worksheet>
 </file>
 
@@ -30921,7 +31122,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -30987,7 +31188,7 @@
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B3" s="7">
         <v>1</v>
@@ -30996,45 +31197,45 @@
         <v>17</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>32</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="K3" s="7">
         <v>3</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B4" s="9">
         <v>1</v>
@@ -31043,45 +31244,45 @@
         <v>28</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>32</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="K4" s="9">
         <v>3</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="B5" s="7">
         <v>1</v>
@@ -31090,45 +31291,45 @@
         <v>17</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="K5" s="7">
         <v>4</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="B6" s="9">
         <v>1</v>
@@ -31137,45 +31338,45 @@
         <v>28</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="K6" s="9">
         <v>4</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="B7" s="7">
         <v>1</v>
@@ -31187,42 +31388,42 @@
         <v>95</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="K7" s="7">
         <v>7</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>142</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B8" s="11">
         <v>1</v>
@@ -31231,45 +31432,45 @@
         <v>17</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="K8" s="11">
         <v>2</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="B9" s="7">
         <v>1</v>
@@ -31278,10 +31479,10 @@
         <v>17</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>20</v>
@@ -31293,30 +31494,30 @@
         <v>52</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="K9" s="7">
         <v>2</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="B10" s="11">
         <v>1</v>
@@ -31325,10 +31526,10 @@
         <v>17</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>50</v>
@@ -31340,30 +31541,30 @@
         <v>89</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="K10" s="11">
         <v>3</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="B11" s="13">
         <v>1</v>
@@ -31372,10 +31573,10 @@
         <v>17</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>20</v>
@@ -31387,25 +31588,25 @@
         <v>76</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="K11" s="13">
         <v>1</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -34851,7 +35052,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -34917,7 +35118,7 @@
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="B3" s="13">
         <v>1</v>
@@ -34926,40 +35127,40 @@
         <v>17</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="K3" s="13">
         <v>4</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -38377,7 +38578,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O227"/>
+  <dimension ref="A1:O228"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -38398,7 +38599,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -38464,7 +38665,7 @@
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="B3" s="7">
         <v>1</v>
@@ -38473,45 +38674,45 @@
         <v>17</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K3" s="7">
         <v>0</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="B4" s="9">
         <v>1</v>
@@ -38520,45 +38721,45 @@
         <v>28</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K4" s="9">
         <v>0</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="B5" s="7">
         <v>1</v>
@@ -38567,45 +38768,45 @@
         <v>17</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K5" s="7">
         <v>0</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="B6" s="11">
         <v>1</v>
@@ -38614,45 +38815,45 @@
         <v>17</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K6" s="11">
         <v>0</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B7" s="7">
         <v>1</v>
@@ -38661,45 +38862,45 @@
         <v>17</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K7" s="7">
         <v>0</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="N7" s="7" t="s">
         <v>37</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B8" s="11">
         <v>1</v>
@@ -38708,45 +38909,45 @@
         <v>17</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K8" s="11">
         <v>0</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="B9" s="7">
         <v>1</v>
@@ -38755,45 +38956,45 @@
         <v>17</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K9" s="7">
         <v>0</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="B10" s="11">
         <v>1</v>
@@ -38802,45 +39003,45 @@
         <v>17</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K10" s="11">
         <v>0</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="B11" s="7">
         <v>1</v>
@@ -38849,45 +39050,45 @@
         <v>17</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>569</v>
+        <v>146</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>570</v>
+        <v>147</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K11" s="7">
         <v>0</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>428</v>
+        <v>150</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>582</v>
+        <v>675</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
     </row>
     <row r="12" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="B12" s="11">
         <v>1</v>
@@ -38896,45 +39097,45 @@
         <v>17</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>652</v>
+        <v>637</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>340</v>
+        <v>577</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>341</v>
+        <v>578</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>25</v>
+        <v>438</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>670</v>
+        <v>590</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
     </row>
     <row r="13" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="B13" s="7">
         <v>1</v>
@@ -38943,45 +39144,45 @@
         <v>17</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>629</v>
+        <v>660</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>629</v>
+        <v>661</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>673</v>
+        <v>344</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>674</v>
+        <v>345</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K13" s="7">
         <v>0</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>517</v>
+        <v>25</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="B14" s="11">
         <v>1</v>
@@ -38990,45 +39191,45 @@
         <v>17</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K14" s="11">
         <v>0</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>315</v>
+        <v>525</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>257</v>
+        <v>688</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="B15" s="7">
         <v>1</v>
@@ -39037,45 +39238,45 @@
         <v>17</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>684</v>
+        <v>637</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>75</v>
+        <v>691</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>76</v>
+        <v>692</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>637</v>
+        <v>693</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K15" s="7">
         <v>0</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>527</v>
+        <v>150</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>685</v>
+        <v>262</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="B16" s="11">
         <v>1</v>
@@ -39084,45 +39285,45 @@
         <v>17</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>629</v>
+        <v>696</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>688</v>
+        <v>75</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>689</v>
+        <v>76</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>690</v>
+        <v>645</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K16" s="11">
         <v>0</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>315</v>
+        <v>535</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="B17" s="7">
         <v>1</v>
@@ -39131,45 +39332,45 @@
         <v>17</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>51</v>
+        <v>700</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>52</v>
+        <v>701</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>281</v>
+        <v>702</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K17" s="7">
         <v>0</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>354</v>
+        <v>703</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="B18" s="11">
         <v>1</v>
@@ -39178,45 +39379,45 @@
         <v>17</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>649</v>
+        <v>286</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K18" s="11">
         <v>0</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>696</v>
+        <v>358</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
     </row>
     <row r="19" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="B19" s="7">
         <v>1</v>
@@ -39225,45 +39426,45 @@
         <v>17</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>699</v>
+        <v>637</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>700</v>
+        <v>657</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K19" s="7">
         <v>0</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>443</v>
+        <v>150</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
     </row>
     <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="B20" s="11">
         <v>1</v>
@@ -39272,45 +39473,45 @@
         <v>17</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>629</v>
+        <v>711</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>704</v>
+        <v>155</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>705</v>
+        <v>156</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>255</v>
+        <v>712</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K20" s="11">
         <v>0</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>517</v>
+        <v>453</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="21" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B21" s="7">
         <v>1</v>
@@ -39319,45 +39520,45 @@
         <v>17</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>709</v>
+        <v>637</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>147</v>
+        <v>716</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>148</v>
+        <v>717</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>710</v>
+        <v>260</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K21" s="7">
         <v>0</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>711</v>
+        <v>525</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
     </row>
     <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="B22" s="11">
         <v>1</v>
@@ -39366,45 +39567,45 @@
         <v>17</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>629</v>
+        <v>721</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>715</v>
+        <v>155</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>716</v>
+        <v>156</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K22" s="11">
         <v>0</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>451</v>
+        <v>723</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="B23" s="7">
         <v>1</v>
@@ -39413,45 +39614,45 @@
         <v>17</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>721</v>
+        <v>637</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>349</v>
+        <v>727</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>350</v>
+        <v>728</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K23" s="7">
         <v>0</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
     </row>
     <row r="24" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="B24" s="11">
         <v>1</v>
@@ -39460,45 +39661,45 @@
         <v>17</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>726</v>
+        <v>637</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>113</v>
+        <v>353</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>114</v>
+        <v>354</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K24" s="11">
         <v>0</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>315</v>
+        <v>438</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="B25" s="7">
         <v>1</v>
@@ -39507,45 +39708,45 @@
         <v>17</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>629</v>
+        <v>738</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>629</v>
+        <v>739</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K25" s="7">
         <v>0</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>451</v>
+        <v>150</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>385</v>
+        <v>741</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
     </row>
     <row r="26" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="B26" s="11">
         <v>1</v>
@@ -39554,105 +39755,135 @@
         <v>17</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>652</v>
+        <v>637</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="K26" s="11">
         <v>0</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>315</v>
+        <v>424</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>736</v>
+        <v>389</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
     </row>
     <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>738</v>
-      </c>
-      <c r="B27" s="13">
+      <c r="A27" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="B27" s="7">
         <v>1</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>629</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>739</v>
-      </c>
-      <c r="F27" s="13" t="s">
+      <c r="D27" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="K27" s="7">
+        <v>0</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>750</v>
+      </c>
+      <c r="B28" s="15">
+        <v>1</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>751</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="13" t="s">
+      <c r="H28" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="I27" s="13" t="s">
-        <v>740</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="K27" s="13">
+      <c r="I28" s="15" t="s">
+        <v>752</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="L27" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="M27" s="13" t="s">
-        <v>552</v>
-      </c>
-      <c r="N27" s="13" t="s">
-        <v>741</v>
-      </c>
-      <c r="O27" s="13" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
+      <c r="L28" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>560</v>
+      </c>
+      <c r="N28" s="15" t="s">
+        <v>753</v>
+      </c>
+      <c r="O28" s="15" t="s">
+        <v>754</v>
+      </c>
     </row>
     <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
@@ -43036,6 +43267,23 @@
       <c r="M227" s="1"/>
       <c r="N227" s="1"/>
       <c r="O227" s="1"/>
+    </row>
+    <row r="228" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="1"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
+      <c r="E228" s="1"/>
+      <c r="F228" s="1"/>
+      <c r="G228" s="1"/>
+      <c r="H228" s="1"/>
+      <c r="I228" s="1"/>
+      <c r="J228" s="1"/>
+      <c r="K228" s="1"/>
+      <c r="L228" s="1"/>
+      <c r="M228" s="1"/>
+      <c r="N228" s="1"/>
+      <c r="O228" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -43067,9 +43315,10 @@
     <hyperlink ref="O25" r:id="rId23"/>
     <hyperlink ref="O26" r:id="rId24"/>
     <hyperlink ref="O27" r:id="rId25"/>
+    <hyperlink ref="O28" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId27"/>
+  <legacyDrawing r:id="rId28"/>
 </worksheet>
 </file>